--- a/GATEWAY/A1#111#MEDIBRIDGEXX/InnovaTeraSolutions/MEDIBRIDGE/1.0/accreditamento-checklist_V9.0.0.xlsx
+++ b/GATEWAY/A1#111#MEDIBRIDGEXX/InnovaTeraSolutions/MEDIBRIDGE/1.0/accreditamento-checklist_V9.0.0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Startup\DigitalTwin\Accreditamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438BFF20-CE47-4EBF-BCCE-F3065ECF2FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCC0CB1-23FC-4989-B16F-07136E6CEF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="230">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -910,59 +910,62 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 23" riportata nei documenti "casi di test RSA" e "CDA2_Referto_di_Radiologia_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
+    <t>Puó essere solo dovuto ad un timeout di rete lato gateway, l'applicativo é in HA</t>
+  </si>
+  <si>
+    <t>24/3/2026T19:16:15</t>
+  </si>
+  <si>
+    <t>24/3/2026T19:21:19</t>
+  </si>
+  <si>
+    <t>24/3/2026T19:24:38</t>
+  </si>
+  <si>
+    <t>28/03/2026T09:07:34</t>
+  </si>
+  <si>
+    <t>28/03/2026T09:12:11</t>
+  </si>
+  <si>
+    <t>28/03/2026T09:21:31</t>
+  </si>
+  <si>
+    <t>28/03/2026T09:23:04</t>
+  </si>
+  <si>
+    <t>a0be68a5c1e0be9ba352167b251a4089</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.020e9c11ad^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>c802eadccc2650c7e0f50eed99599eae</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.82b88b2369^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>832f9f81666e5e76f2e793e9de5b09d2</t>
+  </si>
+  <si>
+    <t>dbc5fb0603da9f840c8645d53c83ca07</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.0f92185929^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.67fd395655^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>24/3/2026T19:18:56</t>
+  </si>
+  <si>
     <t>Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di testare la gestione degli errori semantici sui Dati (status code 422), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway. 
-I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test RAD" e "Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>Puó essere solo dovuto ad un timeout di rete lato gateway, l'applicativo é in HA</t>
-  </si>
-  <si>
-    <t>24/3/2026T19:16:15</t>
-  </si>
-  <si>
-    <t>24/3/2026T19:21:19</t>
-  </si>
-  <si>
-    <t>24/3/2026T19:24:38</t>
-  </si>
-  <si>
-    <t>28/03/2026T09:07:34</t>
-  </si>
-  <si>
-    <t>28/03/2026T09:12:11</t>
-  </si>
-  <si>
-    <t>28/03/2026T09:21:31</t>
-  </si>
-  <si>
-    <t>28/03/2026T09:23:04</t>
-  </si>
-  <si>
-    <t>a0be68a5c1e0be9ba352167b251a4089</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.020e9c11ad^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>c802eadccc2650c7e0f50eed99599eae</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.82b88b2369^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>832f9f81666e5e76f2e793e9de5b09d2</t>
-  </si>
-  <si>
-    <t>dbc5fb0603da9f840c8645d53c83ca07</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.0f92185929^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.67fd395655^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>24/3/2026T19:18:56</t>
+I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test RSA" e "Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
+  </si>
+  <si>
+    <t>Timeout di rete</t>
   </si>
 </sst>
 </file>
@@ -1615,6 +1618,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1636,9 +1642,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3143,14 +3146,14 @@
       <c r="W1" s="9"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53" t="s">
+      <c r="B2" s="53"/>
+      <c r="C2" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="D2" s="52"/>
+      <c r="D2" s="53"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -3171,14 +3174,14 @@
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="60" t="s">
+      <c r="B3" s="56"/>
+      <c r="C3" s="61" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -3199,12 +3202,12 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="60" t="s">
+      <c r="A4" s="57"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="61" t="s">
         <v>199</v>
       </c>
-      <c r="D4" s="52"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="4"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -3226,12 +3229,12 @@
       <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A5" s="58"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60" t="s">
+      <c r="A5" s="59"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61" t="s">
         <v>200</v>
       </c>
-      <c r="D5" s="52"/>
+      <c r="D5" s="53"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -3252,8 +3255,8 @@
       <c r="W5" s="9"/>
     </row>
     <row r="6" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A6" s="49"/>
-      <c r="B6" s="50"/>
+      <c r="A6" s="50"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="10"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -3408,7 +3411,7 @@
         <v>46105</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H10" s="48" t="s">
         <v>206</v>
@@ -3433,8 +3436,12 @@
       <c r="P10" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
+      <c r="Q10" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="R10" s="29" t="s">
+        <v>189</v>
+      </c>
       <c r="S10" s="29" t="s">
         <v>204</v>
       </c>
@@ -3465,7 +3472,7 @@
         <v>46105</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H11" s="48" t="s">
         <v>202</v>
@@ -3490,8 +3497,12 @@
       <c r="P11" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
+      <c r="Q11" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="R11" s="29" t="s">
+        <v>189</v>
+      </c>
       <c r="S11" s="29" t="s">
         <v>204</v>
       </c>
@@ -3522,7 +3533,7 @@
         <v>46105</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H12" s="48" t="s">
         <v>208</v>
@@ -3547,8 +3558,12 @@
       <c r="P12" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
+      <c r="Q12" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="R12" s="29" t="s">
+        <v>189</v>
+      </c>
       <c r="S12" s="29" t="s">
         <v>204</v>
       </c>
@@ -3579,7 +3594,7 @@
         <v>46105</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H13" s="48" t="s">
         <v>209</v>
@@ -3604,8 +3619,12 @@
       <c r="P13" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
+      <c r="Q13" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="R13" s="29" t="s">
+        <v>189</v>
+      </c>
       <c r="S13" s="29" t="s">
         <v>204</v>
       </c>
@@ -3643,15 +3662,29 @@
         <v>153</v>
       </c>
       <c r="L14" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
+        <v>211</v>
+      </c>
+      <c r="M14" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="N14" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="O14" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="P14" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q14" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="R14" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="S14" s="29" t="s">
+        <v>204</v>
+      </c>
       <c r="T14" s="29"/>
       <c r="U14" s="30" t="s">
         <v>60</v>
@@ -3688,15 +3721,29 @@
         <v>153</v>
       </c>
       <c r="L15" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
+        <v>211</v>
+      </c>
+      <c r="M15" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="O15" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="P15" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q15" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="R15" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="S15" s="29" t="s">
+        <v>204</v>
+      </c>
       <c r="T15" s="29"/>
       <c r="U15" s="30" t="s">
         <v>60</v>
@@ -4363,7 +4410,7 @@
     </row>
     <row r="32" spans="1:23" ht="11.1" customHeight="1" thickBot="1">
       <c r="A32" s="27">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="B32" s="27" t="s">
         <v>42</v>
@@ -4375,7 +4422,7 @@
         <v>94</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="F32" s="28"/>
       <c r="G32" s="28"/>
@@ -4996,13 +5043,13 @@
         <v>46109</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="H47" s="61" t="s">
+        <v>215</v>
+      </c>
+      <c r="H47" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="I47" s="49" t="s">
         <v>220</v>
-      </c>
-      <c r="I47" s="61" t="s">
-        <v>221</v>
       </c>
       <c r="J47" s="29" t="s">
         <v>60</v>
@@ -5043,13 +5090,13 @@
         <v>46109</v>
       </c>
       <c r="G48" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="H48" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="H48" s="49" t="s">
+        <v>221</v>
+      </c>
+      <c r="I48" s="49" t="s">
         <v>222</v>
-      </c>
-      <c r="I48" s="61" t="s">
-        <v>223</v>
       </c>
       <c r="J48" s="29" t="s">
         <v>60</v>
@@ -5213,13 +5260,13 @@
         <v>46109</v>
       </c>
       <c r="G52" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="H52" s="61" t="s">
-        <v>224</v>
-      </c>
-      <c r="I52" s="61" t="s">
-        <v>226</v>
+        <v>217</v>
+      </c>
+      <c r="H52" s="49" t="s">
+        <v>223</v>
+      </c>
+      <c r="I52" s="49" t="s">
+        <v>225</v>
       </c>
       <c r="J52" s="29" t="s">
         <v>60</v>
@@ -5260,13 +5307,13 @@
         <v>46109</v>
       </c>
       <c r="G53" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="H53" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="I53" s="61" t="s">
-        <v>227</v>
+        <v>218</v>
+      </c>
+      <c r="H53" s="49" t="s">
+        <v>224</v>
+      </c>
+      <c r="I53" s="49" t="s">
+        <v>226</v>
       </c>
       <c r="J53" s="29" t="s">
         <v>60</v>
@@ -9898,12 +9945,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10171,21 +10221,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10210,18 +10266,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/A1#111#MEDIBRIDGEXX/InnovaTeraSolutions/MEDIBRIDGE/1.0/accreditamento-checklist_V9.0.0.xlsx
+++ b/GATEWAY/A1#111#MEDIBRIDGEXX/InnovaTeraSolutions/MEDIBRIDGE/1.0/accreditamento-checklist_V9.0.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Startup\DigitalTwin\Accreditamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCC0CB1-23FC-4989-B16F-07136E6CEF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E02A1A6-2615-49D9-B584-CA6929245ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -922,42 +922,6 @@
     <t>24/3/2026T19:24:38</t>
   </si>
   <si>
-    <t>28/03/2026T09:07:34</t>
-  </si>
-  <si>
-    <t>28/03/2026T09:12:11</t>
-  </si>
-  <si>
-    <t>28/03/2026T09:21:31</t>
-  </si>
-  <si>
-    <t>28/03/2026T09:23:04</t>
-  </si>
-  <si>
-    <t>a0be68a5c1e0be9ba352167b251a4089</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.020e9c11ad^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>c802eadccc2650c7e0f50eed99599eae</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.82b88b2369^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>832f9f81666e5e76f2e793e9de5b09d2</t>
-  </si>
-  <si>
-    <t>dbc5fb0603da9f840c8645d53c83ca07</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.0f92185929^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.67fd395655^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>24/3/2026T19:18:56</t>
   </si>
   <si>
@@ -966,6 +930,42 @@
   </si>
   <si>
     <t>Timeout di rete</t>
+  </si>
+  <si>
+    <t>51743781e305fd40a81ba42616183c96</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.03cfbe368a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>01/04/2026T21:52:23</t>
+  </si>
+  <si>
+    <t>01/04/2026T21:54:36</t>
+  </si>
+  <si>
+    <t>474689bfbfe1d3dab38e2d54d7e62bac</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.77c6462407^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>66a8c067f3a04f41a36db2dc07eca5bc</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.44c69e7cac^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>01/04/2026T22:10:41</t>
+  </si>
+  <si>
+    <t>98cf12c20bb20c08e2b3be1fe4f52cff</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.a763856686^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>01/04/2026T22:11:46</t>
   </si>
 </sst>
 </file>
@@ -975,7 +975,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1090,12 +1090,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1618,9 +1612,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1642,6 +1633,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3146,14 +3140,14 @@
       <c r="W1" s="9"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54" t="s">
+      <c r="B2" s="52"/>
+      <c r="C2" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="D2" s="53"/>
+      <c r="D2" s="52"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -3174,14 +3168,14 @@
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="61" t="s">
+      <c r="B3" s="55"/>
+      <c r="C3" s="60" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="53"/>
+      <c r="D3" s="52"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -3202,12 +3196,12 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A4" s="57"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="61" t="s">
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="60" t="s">
         <v>199</v>
       </c>
-      <c r="D4" s="53"/>
+      <c r="D4" s="52"/>
       <c r="E4" s="4"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -3229,12 +3223,12 @@
       <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A5" s="59"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61" t="s">
+      <c r="A5" s="58"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="D5" s="53"/>
+      <c r="D5" s="52"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -3255,8 +3249,8 @@
       <c r="W5" s="9"/>
     </row>
     <row r="6" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A6" s="50"/>
-      <c r="B6" s="51"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="50"/>
       <c r="C6" s="10"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -3472,7 +3466,7 @@
         <v>46105</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="H11" s="48" t="s">
         <v>202</v>
@@ -3671,7 +3665,7 @@
         <v>60</v>
       </c>
       <c r="O14" s="29" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="P14" s="29" t="s">
         <v>189</v>
@@ -3730,7 +3724,7 @@
         <v>60</v>
       </c>
       <c r="O15" s="29" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="P15" s="29" t="s">
         <v>189</v>
@@ -4422,7 +4416,7 @@
         <v>94</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F32" s="28"/>
       <c r="G32" s="28"/>
@@ -5040,16 +5034,16 @@
         <v>125</v>
       </c>
       <c r="F47" s="28">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="H47" s="49" t="s">
+        <v>220</v>
+      </c>
+      <c r="H47" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="I47" s="48" t="s">
         <v>219</v>
-      </c>
-      <c r="I47" s="49" t="s">
-        <v>220</v>
       </c>
       <c r="J47" s="29" t="s">
         <v>60</v>
@@ -5087,16 +5081,16 @@
         <v>127</v>
       </c>
       <c r="F48" s="28">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="G48" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="H48" s="49" t="s">
         <v>221</v>
       </c>
-      <c r="I48" s="49" t="s">
+      <c r="H48" s="48" t="s">
         <v>222</v>
+      </c>
+      <c r="I48" s="48" t="s">
+        <v>223</v>
       </c>
       <c r="J48" s="29" t="s">
         <v>60</v>
@@ -5134,7 +5128,6 @@
         <v>129</v>
       </c>
       <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
       <c r="H49" s="27"/>
       <c r="I49" s="27"/>
       <c r="J49" s="29" t="s">
@@ -5257,15 +5250,15 @@
         <v>135</v>
       </c>
       <c r="F52" s="28">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="G52" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="H52" s="49" t="s">
-        <v>223</v>
-      </c>
-      <c r="I52" s="49" t="s">
+        <v>226</v>
+      </c>
+      <c r="H52" s="48" t="s">
+        <v>224</v>
+      </c>
+      <c r="I52" s="48" t="s">
         <v>225</v>
       </c>
       <c r="J52" s="29" t="s">
@@ -5304,16 +5297,16 @@
         <v>137</v>
       </c>
       <c r="F53" s="28">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="G53" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="H53" s="49" t="s">
-        <v>224</v>
-      </c>
-      <c r="I53" s="49" t="s">
-        <v>226</v>
+        <v>229</v>
+      </c>
+      <c r="H53" s="48" t="s">
+        <v>227</v>
+      </c>
+      <c r="I53" s="48" t="s">
+        <v>228</v>
       </c>
       <c r="J53" s="29" t="s">
         <v>60</v>
@@ -9945,15 +9938,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10221,27 +10211,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10266,9 +10250,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/A1#111#MEDIBRIDGEXX/InnovaTeraSolutions/MEDIBRIDGE/1.0/accreditamento-checklist_V9.0.0.xlsx
+++ b/GATEWAY/A1#111#MEDIBRIDGEXX/InnovaTeraSolutions/MEDIBRIDGE/1.0/accreditamento-checklist_V9.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Startup\DigitalTwin\Accreditamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E02A1A6-2615-49D9-B584-CA6929245ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55F935B-1493-438F-9058-D2E1940BEDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -932,40 +932,40 @@
     <t>Timeout di rete</t>
   </si>
   <si>
-    <t>51743781e305fd40a81ba42616183c96</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.03cfbe368a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>01/04/2026T21:52:23</t>
-  </si>
-  <si>
-    <t>01/04/2026T21:54:36</t>
-  </si>
-  <si>
-    <t>474689bfbfe1d3dab38e2d54d7e62bac</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.77c6462407^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>66a8c067f3a04f41a36db2dc07eca5bc</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.44c69e7cac^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>01/04/2026T22:10:41</t>
-  </si>
-  <si>
-    <t>98cf12c20bb20c08e2b3be1fe4f52cff</t>
-  </si>
-  <si>
-    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.a763856686^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>01/04/2026T22:11:46</t>
+    <t>e027ad2b34f348b416818b7f313a0157</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.9cec6e8551^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>09/04/2026T20:03:43</t>
+  </si>
+  <si>
+    <t>5d4e4e7a6529bf11fc41f43c5de4eb09</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.caf76ef2f7^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>09/04/2026T20:07:04</t>
+  </si>
+  <si>
+    <t>68d949e35ad34f7b9051d92e1417bee5</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.1de80fb597^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>09/04/2026T20:11:12</t>
+  </si>
+  <si>
+    <t>7e2bd8e6ae3d45859504176f19f338f3</t>
+  </si>
+  <si>
+    <t>IT-REG-LOM-01.1f2714c26a31f53a7de0221ad47cd5d24a96ebf759286393a89723d2697fe25e.a56fa87d14^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>09/04/2026T20:14:17</t>
   </si>
 </sst>
 </file>
@@ -975,7 +975,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1090,6 +1090,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1634,8 +1641,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5034,12 +5041,12 @@
         <v>125</v>
       </c>
       <c r="F47" s="28">
-        <v>46113</v>
+        <v>46121</v>
       </c>
       <c r="G47" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="H47" s="61" t="s">
+      <c r="H47" s="48" t="s">
         <v>218</v>
       </c>
       <c r="I47" s="48" t="s">
@@ -5081,16 +5088,16 @@
         <v>127</v>
       </c>
       <c r="F48" s="28">
-        <v>46113</v>
+        <v>46121</v>
       </c>
       <c r="G48" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="H48" s="48" t="s">
         <v>221</v>
       </c>
-      <c r="H48" s="48" t="s">
+      <c r="I48" s="48" t="s">
         <v>222</v>
-      </c>
-      <c r="I48" s="48" t="s">
-        <v>223</v>
       </c>
       <c r="J48" s="29" t="s">
         <v>60</v>
@@ -5250,7 +5257,7 @@
         <v>135</v>
       </c>
       <c r="F52" s="28">
-        <v>46113</v>
+        <v>46121</v>
       </c>
       <c r="G52" s="28" t="s">
         <v>226</v>
@@ -5297,7 +5304,7 @@
         <v>137</v>
       </c>
       <c r="F53" s="28">
-        <v>46113</v>
+        <v>46121</v>
       </c>
       <c r="G53" s="28" t="s">
         <v>229</v>
@@ -5451,7 +5458,7 @@
     </row>
     <row r="58" spans="1:23" ht="14.25" customHeight="1">
       <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
+      <c r="G58" s="61"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
       <c r="J58" s="7"/>
@@ -9938,12 +9945,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10211,21 +10221,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10250,18 +10266,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
